--- a/02table/TableS8_GWAS_for_SBEIIa_Zm00001d003817.xlsx
+++ b/02table/TableS8_GWAS_for_SBEIIa_Zm00001d003817.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8B1154-EB38-EA41-B8E9-3327BC0DA350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB39104A-9825-4E41-9133-4A5DE0D17B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="72080" yWindow="1160" windowWidth="30240" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1888,7 +1888,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Table S8 eQTLs for gene expression of </t>
+      <t xml:space="preserve">Table S8. eQTLs for gene expression of </t>
     </r>
     <r>
       <rPr>
